--- a/artfynd/Björnberget N artfynd.xlsx
+++ b/artfynd/Björnberget N artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120122588</v>
+        <v>120122581</v>
       </c>
       <c r="B2" t="n">
-        <v>80111</v>
+        <v>93213</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6461</v>
+        <v>2059</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>685070</v>
+        <v>684965</v>
       </c>
       <c r="R2" t="n">
-        <v>7093846</v>
+        <v>7093978</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,45 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56822973</v>
+        <v>120122583</v>
       </c>
       <c r="B3" t="n">
-        <v>92535</v>
+        <v>93191</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Björnberget norr, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>685867</v>
+        <v>685155</v>
       </c>
       <c r="R3" t="n">
-        <v>7093653</v>
+        <v>7093876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -853,31 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120122586</v>
+        <v>16944450</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>685118</v>
+        <v>685297</v>
       </c>
       <c r="R4" t="n">
-        <v>7093851</v>
+        <v>7093922</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -939,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -959,26 +954,26 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120148068</v>
+        <v>120122585</v>
       </c>
       <c r="B5" t="n">
-        <v>92535</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>685560</v>
+        <v>685129</v>
       </c>
       <c r="R5" t="n">
-        <v>7093731</v>
+        <v>7093866</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1036,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,45 +1063,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56822964</v>
+        <v>120122586</v>
       </c>
       <c r="B6" t="n">
-        <v>78647</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Björnberget norr, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685522</v>
+        <v>685118</v>
       </c>
       <c r="R6" t="n">
-        <v>7093524</v>
+        <v>7093851</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1133,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1149,58 +1144,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>gammal tallåga</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120148067</v>
+        <v>120122588</v>
       </c>
       <c r="B7" t="n">
-        <v>78980</v>
+        <v>80460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6461</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>685698</v>
+        <v>685070</v>
       </c>
       <c r="R7" t="n">
-        <v>7093811</v>
+        <v>7093846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1240,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56822972</v>
+        <v>56822968</v>
       </c>
       <c r="B8" t="n">
-        <v>79012</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1283,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>685836</v>
+        <v>685703</v>
       </c>
       <c r="R8" t="n">
-        <v>7093589</v>
+        <v>7093493</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1361,7 +1346,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asplåga</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1379,48 +1364,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>16944450</v>
+        <v>56822972</v>
       </c>
       <c r="B9" t="n">
-        <v>92535</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Björnberget norr, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>685297</v>
+        <v>685836</v>
       </c>
       <c r="R9" t="n">
-        <v>7093922</v>
+        <v>7093589</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1444,12 +1429,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1460,26 +1445,36 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56822971</v>
+        <v>16944461</v>
       </c>
       <c r="B10" t="n">
-        <v>79598</v>
+        <v>78993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1487,37 +1482,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Björnberget norr, Ång</t>
+          <t>Grundtjärn, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>685687</v>
+        <v>685565</v>
       </c>
       <c r="R10" t="n">
-        <v>7093554</v>
+        <v>7093527</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1541,12 +1536,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2014-08-29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,70 +1553,80 @@
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>låga</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>silverstubbe/dimensionsstubbe</t>
+          <t>Pinus sylvestris # låga</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>69298999</v>
+        <v>56822964</v>
       </c>
       <c r="B11" t="n">
-        <v>91406</v>
+        <v>78993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Grundtjärnen, Ång</t>
+          <t>Björnberget norr, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>685500</v>
+        <v>685522</v>
       </c>
       <c r="R11" t="n">
-        <v>7093566</v>
+        <v>7093524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,17 +1653,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-09-02</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-09-02</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,78 +1675,65 @@
           <t>barrnaturskog</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallåga # Pinus sylvestris</t>
+          <t>gammal tallåga</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>56822967</v>
+        <v>69298997</v>
       </c>
       <c r="B12" t="n">
-        <v>95594</v>
+        <v>78993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Björnberget norr, Ång</t>
+          <t>Grundtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>685697</v>
+        <v>685558</v>
       </c>
       <c r="R12" t="n">
-        <v>7093433</v>
+        <v>7093541</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1773,12 +1760,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2017-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2017-09-02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1793,49 +1785,67 @@
       <c r="AI12" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>16944461</v>
+        <v>16944532</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>92083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1845,10 +1855,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>685565</v>
+        <v>685540</v>
       </c>
       <c r="R13" t="n">
-        <v>7093527</v>
+        <v>7093531</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1927,32 +1937,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>69298998</v>
+        <v>69298999</v>
       </c>
       <c r="B14" t="n">
-        <v>5492</v>
+        <v>92083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>101410</v>
+        <v>1503</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1972,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>685526</v>
+        <v>685500</v>
       </c>
       <c r="R14" t="n">
-        <v>7093627</v>
+        <v>7093566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2044,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>1 substratenheter # tall # Pinus sylvestris</t>
+          <t>1 substratenheter # tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2052,45 +2062,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>69298997</v>
+        <v>56822967</v>
       </c>
       <c r="B15" t="n">
-        <v>78647</v>
+        <v>96338</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>2809</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Grundtjärnen, Ång</t>
+          <t>Björnberget norr, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>685558</v>
+        <v>685697</v>
       </c>
       <c r="R15" t="n">
-        <v>7093541</v>
+        <v>7093433</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,17 +2127,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2017-09-02</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2017-09-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,45 +2147,27 @@
       <c r="AI15" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AN15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>1 substratenheter # tallåga # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>56822968</v>
+        <v>56822973</v>
       </c>
       <c r="B16" t="n">
-        <v>96614</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2188,21 +2175,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2212,10 +2199,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685703</v>
+        <v>685867</v>
       </c>
       <c r="R16" t="n">
-        <v>7093493</v>
+        <v>7093653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2262,11 +2249,6 @@
       <c r="AI16" t="inlineStr">
         <is>
           <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>asplåga</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2284,10 +2266,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>56822970</v>
+        <v>120148068</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,34 +2277,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Björnberget norr, Ång</t>
+          <t>Bjurholm, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>685695</v>
+        <v>685560</v>
       </c>
       <c r="R17" t="n">
-        <v>7093500</v>
+        <v>7093731</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2349,12 +2331,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2365,71 +2347,61 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>barrnaturskog</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Hanna Bäckman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120122581</v>
+        <v>56822963</v>
       </c>
       <c r="B18" t="n">
-        <v>92551</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget norr, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684965</v>
+        <v>685563</v>
       </c>
       <c r="R18" t="n">
-        <v>7093978</v>
+        <v>7093521</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2456,12 +2428,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2472,26 +2444,36 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>tallåga</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>56822969</v>
+        <v>56822971</v>
       </c>
       <c r="B19" t="n">
-        <v>80083</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2499,21 +2481,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2523,10 +2505,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>685698</v>
+        <v>685687</v>
       </c>
       <c r="R19" t="n">
-        <v>7093501</v>
+        <v>7093554</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2577,7 +2559,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>silverstubbe/dimensionsstubbe</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2595,10 +2577,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120122583</v>
+        <v>56822969</v>
       </c>
       <c r="B20" t="n">
-        <v>92529</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,34 +2588,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bjurholm, Ång</t>
+          <t>Björnberget norr, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685155</v>
+        <v>685698</v>
       </c>
       <c r="R20" t="n">
-        <v>7093876</v>
+        <v>7093501</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2660,12 +2642,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2676,64 +2658,74 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Hanna Bäckman</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16944532</v>
+        <v>56822970</v>
       </c>
       <c r="B21" t="n">
-        <v>91406</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Grundtjärn, Ång</t>
+          <t>Björnberget norr, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>685540</v>
+        <v>685695</v>
       </c>
       <c r="R21" t="n">
-        <v>7093531</v>
+        <v>7093500</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2757,12 +2749,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2015-05-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2014-08-29</t>
+          <t>2015-10-30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2774,80 +2766,70 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>låga</t>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # låga</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56822963</v>
+        <v>69298998</v>
       </c>
       <c r="B22" t="n">
-        <v>91210</v>
+        <v>5495</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>101410</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnberget norr, Ång</t>
+          <t>Grundtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685563</v>
+        <v>685526</v>
       </c>
       <c r="R22" t="n">
-        <v>7093521</v>
+        <v>7093627</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2874,12 +2856,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2015-05-18</t>
+          <t>2017-09-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2015-10-30</t>
+          <t>2017-09-02</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Observerad och artbestämd av Ulrika Westling. Inrapporterad av Johan Kjetselberg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2896,52 +2883,65 @@
           <t>barrnaturskog</t>
         </is>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AN22" t="n">
+        <v>1</v>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>tallåga</t>
+          <t>1 substratenheter # tall # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120122585</v>
+        <v>120148067</v>
       </c>
       <c r="B23" t="n">
-        <v>92535</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685129</v>
+        <v>685698</v>
       </c>
       <c r="R23" t="n">
-        <v>7093866</v>
+        <v>7093811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-29</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AD23" t="b">
